--- a/CBT_2023_3회/산업안전기사_2023_3회_문항등록.xlsx
+++ b/CBT_2023_3회/산업안전기사_2023_3회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="U8" s="32" t="inlineStr">
         <is>
-          <t>ABE종 안전모에 대하여 내수성 시험을 할 때 물에 담그기 전의 질량이 400g 이고, 물에 담근 후의 질량이 410g 이었다면 질량증가율과 합격여부로 옳은 것은?</t>
+          <t>ABE종 안전모에 대하여 내수성 시험을 할 때 물에 담그기 전의 질량이 400g이고, 물에 담근 후의 질량이 410g 이었다면 질량증가율과 합격여부로 옳은 것은?</t>
         </is>
       </c>
       <c r="V8" s="32" t="inlineStr"/>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="AG8" s="32" t="inlineStr">
         <is>
-          <t>$\text{질량증가율} = \dfrac{410 - 400}{400} \times 100 = 2.5$ [%] 다. &lt;strong&gt;기준은 1 [%] 미만&lt;/strong&gt;이므로 &lt;strong&gt;불합격&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 내수성 시험&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;내용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AE · ABE종&lt;/u&gt; (내전압성이 있는 것)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 ~ 25 [℃] 물에 24시간 담근다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{담근 뒤 질량} - \text{담그기 전 질량}}{\text{담그기 전 질량}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [%] 는 불합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{질량증가율} = \dfrac{410 - 400}{400} \times 100 = 2.5$ [%]다. &lt;strong&gt;기준은 1 [%] 미만&lt;/strong&gt;이므로 &lt;strong&gt;불합격&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 내수성 시험&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;내용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;AE · ABE종&lt;/u&gt; (내전압성이 있는 것)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 ~ 25 [℃] 물에 24시간 담근다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{담근 뒤 질량} - \text{담그기 전 질량}}{\text{담그기 전 질량}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [%]는 불합격&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>② 2.5 [%] 는 맞지만 1 [%] 미만이 아니므로 합격이 아니다.&lt;br&gt;③ 102.5 [%] 는 증가율이 아니라 담근 뒤의 비율이다.&lt;br&gt;④ 102.5 [%] 라는 값 자체가 어긋난다.</t>
+          <t>② 2.5 [%]는 맞지만 1 [%] 미만이 아니므로 합격이 아니다.&lt;br&gt;③ 102.5 [%]는 증가율이 아니라 담근 뒤의 비율이다.&lt;br&gt;④ 102.5 [%]라는 값 자체가 어긋난다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AG10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;P 는 Person(개체)&lt;/strong&gt;다. &lt;strong&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/strong&gt;를 뜻한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러나는 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function 함수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;P 와 E 가 함께 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person 개체(사람)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;P는 Person(개체)&lt;/strong&gt;다. &lt;strong&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/strong&gt;를 뜻한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러나는 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function 함수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;P와 E가 함께 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person 개체(사람)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH10" s="32" t="inlineStr">
         <is>
-          <t>② 인간의 행동은 B 다.&lt;br&gt;③ 심리적 환경은 E 다.&lt;br&gt;④ 인간관계도 E 에 든다.</t>
+          <t>② 인간의 행동은 B다.&lt;br&gt;③ 심리적 환경은 E다.&lt;br&gt;④ 인간관계도 E에 든다.</t>
         </is>
       </c>
       <c r="AI10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈(Lewin)의 인간 행동 법칙&lt;/strong&gt;&lt;br&gt;이 식의 요지는 &lt;strong&gt;행동은 사람 탓만도 환경 탓만도 아니다&lt;/strong&gt;라는 것이다. &lt;strong&gt;사람은 쉽게 못 바꾸지만 환경은 바꿀 수&lt;/strong&gt; 있으므로, 안전관리는 &lt;strong&gt;E 를 손보는 쪽&lt;/strong&gt;으로 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P 는 개체, E 는 환경&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈(Lewin)의 인간 행동 법칙&lt;/strong&gt;&lt;br&gt;이 식의 요지는 &lt;strong&gt;행동은 사람 탓만도 환경 탓만도 아니다&lt;/strong&gt;라는 것이다. &lt;strong&gt;사람은 쉽게 못 바꾸지만 환경은 바꿀 수&lt;/strong&gt; 있으므로, 안전관리는 &lt;strong&gt;E를 손보는 쪽&lt;/strong&gt;으로 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P는 개체, E는 환경&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AG11" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;목표에 의한 관리(MBO)는 Y이론&lt;/strong&gt;의 처방이다. 나머지 셋은 X·Y 가 뒤바뀌었다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;X이론과 Y이론의 관리 처방&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;X이론&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Y이론&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;사람을 보는 눈&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게으르고 일을 싫어한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일을 즐기고 스스로 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;처방&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;권위주의적 리더십 · 경제적 보상체계의 강화 · 명령과 통제 · 상부책임제도의 강화 · 면밀한 감독&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;목표에 의한 관리(MBO) · 직무의 확장 · 분권화와 권한의 위임 · 비공식적 조직의 활용 · 자율통제&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;목표에 의한 관리(MBO)는 Y이론&lt;/strong&gt;의 처방이다. 나머지 셋은 X·Y가 뒤바뀌었다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;X이론과 Y이론의 관리 처방&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;X이론&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Y이론&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;사람을 보는 눈&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게으르고 일을 싫어한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일을 즐기고 스스로 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;처방&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;권위주의적 리더십 · 경제적 보상체계의 강화 · 명령과 통제 · 상부책임제도의 강화 · 면밀한 감독&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;목표에 의한 관리(MBO) · 직무의 확장 · 분권화와 권한의 위임 · 비공식적 조직의 활용 · 자율통제&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH11" s="32" t="inlineStr">
@@ -2898,17 +2898,17 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;다수를 조직적으로 훈련&lt;/strong&gt; 하는 것은 Off JT 의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 상호신뢰와 이해가 깊어진다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 조직적으로 · 전문가 초빙 · 특별한 교재와 설비 · 여러 직장의 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;다수를 조직적으로 훈련&lt;/strong&gt;하는 것은 Off JT의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 상호신뢰와 이해가 깊어진다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 조직적으로 · 전문가 초빙 · 특별한 교재와 설비 · 여러 직장의 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>② 개개인에게 맞춘 지도훈련은 OJT 의 특징이다.&lt;br&gt;③ 상호 신뢰와 이해도가 높아지는 것도 그렇다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련도 그렇다.</t>
+          <t>② 개개인에게 맞춘 지도훈련은 OJT의 특징이다.&lt;br&gt;③ 상호 신뢰와 이해도가 높아지는 것도 그렇다.&lt;br&gt;④ 직장 실정에 맞는 실제적 훈련도 그렇다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「많이 · 조직적으로 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 신뢰 · 실정」은 OJT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수를 조직적으로면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「많이 · 조직적으로 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 신뢰 · 실정」은 OJT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수를 조직적으로면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AI16" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;브레인스토밍의 4원칙&lt;/strong&gt;&lt;br&gt;네 원칙을 &lt;strong&gt;비 · 자 · 대 · 수&lt;/strong&gt;로 새긴다. &lt;strong&gt;네 보기가 원칙 하나씩에 대응&lt;/strong&gt; 하도록 짜여 있고, &lt;strong&gt;셋은 어긋나게 하나만 맞게&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비판 금지 · 자유 분방 · 대량 발언 · 수정 발언&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;브레인스토밍의 4원칙&lt;/strong&gt;&lt;br&gt;네 원칙을 &lt;strong&gt;비 · 자 · 대 · 수&lt;/strong&gt;로 새긴다. &lt;strong&gt;네 보기가 원칙 하나씩에 대응&lt;/strong&gt;하도록 짜여 있고, &lt;strong&gt;셋은 어긋나게 하나만 맞게&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비판 금지 · 자유 분방 · 대량 발언 · 수정 발언&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AG18" s="32" t="inlineStr">
         <is>
-          <t>자율검사프로그램은 &lt;strong&gt;안전검사 주기의 1/2 마다&lt;/strong&gt; 검사해야 한다. &lt;strong&gt;같은 주기가 아니라 두 배 자주&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;자율검사프로그램의 인정 요건 (규칙 제132조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검사원을 고용하고 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검사를 할 수 있는 장비를 갖추고 유지·관리할 수 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전검사 주기의 1/2 에 해당하는 주기마다 검사할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같은 주기가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자율검사프로그램의 검사기준이 안전검사기준을 충족할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>자율검사프로그램은 &lt;strong&gt;안전검사 주기의 1/2 마다&lt;/strong&gt; 검사해야 한다. &lt;strong&gt;같은 주기가 아니라 두 배 자주&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;자율검사프로그램의 인정 요건 (규칙 제132조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검사원을 고용하고 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검사를 할 수 있는 장비를 갖추고 유지·관리할 수 있을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전검사 주기의 1/2에 해당하는 주기마다 검사할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같은 주기가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자율검사프로그램의 검사기준이 안전검사기준을 충족할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH18" s="32" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="U20" s="32" t="inlineStr">
         <is>
-          <t>도수율이 24.5 이고, 강도율이 1.15인 사업장이 있다. 이 사업장에서 한 근로자가 입사하여 퇴직할 때까지 몇 일간의 근로손실일수가 발생하겠는가?</t>
+          <t>도수율이 24.5이고, 강도율이 1.15인 사업장이 있다. 이 사업장에서 한 근로자가 입사하여 퇴직할 때까지 몇 일간의 근로손실일수가 발생하겠는가?</t>
         </is>
       </c>
       <c r="V20" s="32" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>① 2.45일은 도수율을 10 으로 나눈 값(환산도수율)이다.&lt;br&gt;③ 215일은 계산과 맞지 않는다.&lt;br&gt;④ 245일은 도수율에 10 을 곱한 값이다.</t>
+          <t>① 2.45일은 도수율을 10으로 나눈 값(환산도수율)이다.&lt;br&gt;③ 215일은 계산과 맞지 않는다.&lt;br&gt;④ 245일은 도수율에 10을 곱한 값이다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
@@ -3801,17 +3801,17 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>연근로시간은 $450 \times 9 \times 300 = 1 {,} 215 {,} 000$ 시간, 근로손실일수는 $3 {,} 650 \times \dfrac{300}{365} = 3 {,} 000$ 일이다. 도수율 $19.75$, 강도율 $2.47$ 이 나온다.</t>
+          <t>연근로시간은 $450 \times 9 \times 300 = 1 {,} 215 {,} 000$ 시간, 근로손실일수는 $3 {,} 650 \times \dfrac{300}{365} = 3 {,} 000$ 일이다. 도수율 $19.75$, 강도율 $2.47$이 나온다.</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
-          <t>① 0.02 와 2.55 는 도수율에 10⁶ 을 곱하지 않은 값이다.&lt;br&gt;② 0.19 와 0.25 도 자릿수가 어긋난다.&lt;br&gt;④ 20.43 과 2.55 는 휴업일수를 그대로 쓴 값에 가깝다.</t>
+          <t>① 0.02와 2.55는 도수율에 10⁶ 을 곱하지 않은 값이다.&lt;br&gt;② 0.19와 0.25 도 자릿수가 어긋난다.&lt;br&gt;④ 20.43과 2.55는 휴업일수를 그대로 쓴 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;도수율과 강도율&lt;/strong&gt;&lt;br&gt;두 함정이 있다 — &lt;strong&gt;연근로시간에 「1일 시간 × 연 근무일 × 인원」을 모두 곱하는 것&lt;/strong&gt;과, &lt;strong&gt;휴업일수에 300/365 를 곱해 근로손실일수로 바꾸는 것&lt;/strong&gt;이다. 둘 중 하나만 놓쳐도 다른 보기로 빠진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휴업일수 × 300/365 = 근로손실일수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;도수율과 강도율&lt;/strong&gt;&lt;br&gt;두 함정이 있다 — &lt;strong&gt;연근로시간에 「1일 시간 × 연 근무일 × 인원」을 모두 곱하는 것&lt;/strong&gt;과, &lt;strong&gt;휴업일수에 300/365를 곱해 근로손실일수로 바꾸는 것&lt;/strong&gt;이다. 둘 중 하나만 놓쳐도 다른 보기로 빠진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휴업일수 × 300/365 = 근로손실일수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;통상사상&lt;/strong&gt;이다. &lt;strong&gt;집 모양 오각형&lt;/strong&gt;으로 그리며 &lt;strong&gt;늘 일어나는 정상적인 사상&lt;/strong&gt;을 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 분석할 수 있는 사상 — 정상사상과 중간사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 분석할 수 없는 밑바닥 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;자료가 모자라 더 전개하지 않는 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양 오각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;늘 일어나는 정상적인 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 곳으로 이어진다는 표시&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;통상사상&lt;/strong&gt;이다. &lt;strong&gt;집 모양 오각형&lt;/strong&gt;으로 그리며 &lt;strong&gt;늘 일어나는 정상적인 사상&lt;/strong&gt;을 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;모양&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 분석할 수 있는 사상 — 정상사상과 중간사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 분석할 수 없는 밑바닥 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;자료가 모자라 더 전개하지 않는 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양 오각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;늘 일어나는 정상적인 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 곳으로 이어진다는 표시&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 통상사상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;통상사상은 「고장이 아니라 정상」&lt;/strong&gt;인 사상이다 — &lt;strong&gt;전원이 들어와 있다 · 밸브가 열려 있다&lt;/strong&gt; 같은 것이다. &lt;strong&gt;집 모양은 「늘 그 자리에 있다」&lt;/strong&gt;는 뜻으로 새긴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;집 모양은 통상사상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 통상사상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;통상사상은 「고장이 아니라 정상」&lt;/strong&gt;인 사상이다 — &lt;strong&gt;전원이 들어와 있다 · 밸브가 열려 있다&lt;/strong&gt; 같은 것이다. &lt;strong&gt;집 모양은 「늘 그 자리에 있다」&lt;/strong&gt;는 뜻으로 새긴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;집 모양은 통상사상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;확률 중요도&lt;/strong&gt;다. &lt;strong&gt;기본사상의 확률이 조금 바뀔 때 정상사상의 확률이 얼마나 바뀌는가&lt;/strong&gt;를 나타내므로 &lt;strong&gt;편미분계수&lt;/strong&gt;와 같다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 중요도 지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;중요도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구조 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;확률과 무관하게 FT 의 구조만으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;어느 자리가 중요한가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;확률 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상의 확률 변화가 정상사상에 미치는 영향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;편미분계수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;치명 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상의 확률을 몇 [%] 낮추면 정상사상이 몇 [%] 낮아지나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개선 효과의 크기&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;확률 중요도&lt;/strong&gt;다. &lt;strong&gt;기본사상의 확률이 조금 바뀔 때 정상사상의 확률이 얼마나 바뀌는가&lt;/strong&gt;를 나타내므로 &lt;strong&gt;편미분계수&lt;/strong&gt;와 같다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 중요도 지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;중요도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구조 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;확률과 무관하게 FT의 구조만으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;어느 자리가 중요한가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;확률 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상의 확률 변화가 정상사상에 미치는 영향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;편미분계수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;치명 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상의 확률을 몇 [%] 낮추면 정상사상이 몇 [%] 낮아지나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개선 효과의 크기&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AI25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 중요도 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「편미분계수」&lt;/strong&gt;라는 말이 곧 &lt;strong&gt;「한 값이 조금 바뀔 때 결과가 얼마나 바뀌나」&lt;/strong&gt;다. &lt;strong&gt;확률의 변화를 다루므로 확률 중요도&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;편미분계수면 확률 중요도&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 중요도 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「편미분계수」&lt;/strong&gt;라는 말이 곧 &lt;strong&gt;「한 값이 조금 바뀔 때 결과가 얼마나 바뀌나」&lt;/strong&gt;다. &lt;strong&gt;확률의 변화를 다루므로 확률 중요도&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;편미분계수면 확률 중요도&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AG26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;일반화가 가능&lt;/strong&gt; 한 것이 현장 연구의 장점이다. &lt;strong&gt;실제 상황에서 얻은 결과라 그대로 현장에 옮길 수&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;실험실 연구와 현장 연구&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;실험실 연구&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;현장 연구&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;실험조건 조절&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쉽다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;자료의 정확성&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;비용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반화(현실 적용)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;안전성&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;일반화가 가능&lt;/strong&gt;한 것이 현장 연구의 장점이다. &lt;strong&gt;실제 상황에서 얻은 결과라 그대로 현장에 옮길 수&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;실험실 연구와 현장 연구&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;실험실 연구&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;현장 연구&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;실험조건 조절&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쉽다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;자료의 정확성&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;비용&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반화(현실 적용)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;안전성&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH26" s="32" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="AG28" s="32" t="inlineStr">
         <is>
-          <t>$A \cdot A ' = 0$ 이다. &lt;strong&gt;어떤 사상과 그 여사상이 함께 일어날 수는 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불 대수의 주요 정리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;항등법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot 1 = A$, $A + 0 = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지배법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot 0 = 0$, $A + 1 = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①·②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보원법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot A ' = 0$, $A + A ' = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③은 1 이라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흡수법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A ( A + B ) = A$, $A + AB = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동일법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot A = A$, $A + A = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$A \cdot A ' = 0$이다. &lt;strong&gt;어떤 사상과 그 여사상이 함께 일어날 수는 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불 대수의 주요 정리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;항등법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot 1 = A$, $A + 0 = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지배법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot 0 = 0$, $A + 1 = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①·②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보원법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot A ' = 0$, $A + A ' = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③은 1이라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흡수법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A ( A + B ) = A$, $A + AB = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동일법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A \cdot A = A$, $A + A = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>① $A \cdot 0 = 0$ 은 지배법칙으로 맞다.&lt;br&gt;② $A + 1 = 1$ 도 그렇다.&lt;br&gt;④ $A ( A + B ) = A$ 는 흡수법칙으로 맞다.</t>
+          <t>① $A \cdot 0 = 0$은 지배법칙으로 맞다.&lt;br&gt;② $A + 1 = 1$도 그렇다.&lt;br&gt;④ $A ( A + B ) = A$는 흡수법칙으로 맞다.</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① β = 0 이 되는 위치는 없다.&lt;br&gt;② β &amp;lt; 1 은 교차점보다 왼쪽에 기준이 있을 때다.&lt;br&gt;④ β &amp;gt; 1 은 교차점보다 오른쪽에 있을 때다.</t>
+          <t>① β = 0이 되는 위치는 없다.&lt;br&gt;② β &amp;lt; 1은 교차점보다 왼쪽에 기준이 있을 때다.&lt;br&gt;④ β &amp;gt; 1은 교차점보다 오른쪽에 있을 때다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;신호검출이론(SDT)의 반응기준&lt;/strong&gt;&lt;br&gt;$\beta = \dfrac{\text{신호의 확률밀도}}{\text{잡음의 확률밀도}}$ 다. &lt;strong&gt;두 곡선이 만나면 분자와 분모가 같아 1&lt;/strong&gt;이 된다. &lt;strong&gt;네 결과(적중 · 허위경보 · 검출실패 · 정기각)&lt;/strong&gt;도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;교차점이면 β = 1&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;신호검출이론(SDT)의 반응기준&lt;/strong&gt;&lt;br&gt;$\beta = \dfrac{\text{신호의 확률밀도}}{\text{잡음의 확률밀도}}$다. &lt;strong&gt;두 곡선이 만나면 분자와 분모가 같아 1&lt;/strong&gt;이 된다. &lt;strong&gt;네 결과(적중 · 허위경보 · 검출실패 · 정기각)&lt;/strong&gt;도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;교차점이면 β = 1&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;평균 작동시간(MTTF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;총 가동시간은 「개수 × 시간」&lt;/strong&gt;이라는 점이 갈림길이다 — &lt;strong&gt;1,000개를 10만 시간 돌렸으면 10⁸ 시간&lt;/strong&gt;이다. &lt;strong&gt;그것을 고장 수 5 로 나누면&lt;/strong&gt; MTTF 가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MTTF = 총 가동시간 ÷ 고장 건수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;평균 작동시간(MTTF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;총 가동시간은 「개수 × 시간」&lt;/strong&gt;이라는 점이 갈림길이다 — &lt;strong&gt;1,000개를 10만 시간 돌렸으면 10⁸ 시간&lt;/strong&gt;이다. &lt;strong&gt;그것을 고장 수 5로 나누면&lt;/strong&gt; MTTF가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MTTF = 총 가동시간 ÷ 고장 건수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AG34" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;근전도(EMG)&lt;/strong&gt;다. &lt;strong&gt;다리라는 특정 부위&lt;/strong&gt;의 부하를 재려면 &lt;strong&gt;국소적 척도&lt;/strong&gt; 라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업부하의 측정 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 재나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소적 근육 활동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근전도(EMG)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;특정 근육 하나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전신적 육체 부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소소비량 · 에너지소비량 · 심박수 · 혈압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;몸 전체&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정신적 부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;점멸융합주파수 · 뇌전도 · 눈 깜빡임률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;근전도(EMG)&lt;/strong&gt;다. &lt;strong&gt;다리라는 특정 부위&lt;/strong&gt;의 부하를 재려면 &lt;strong&gt;국소적 척도&lt;/strong&gt;라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업부하의 측정 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 재나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소적 근육 활동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근전도(EMG)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;특정 근육 하나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전신적 육체 부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산소소비량 · 에너지소비량 · 심박수 · 혈압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;몸 전체&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정신적 부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;점멸융합주파수 · 뇌전도 · 눈 깜빡임률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH34" s="32" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;열교환의 방법과 온열조건&lt;/strong&gt;&lt;br&gt;$S = M - E \pm R \pm C - W$ 라는 열균형 방정식에서 &lt;strong&gt;증발(E) · 복사(R) · 대류(C)&lt;/strong&gt;가 나온다. &lt;strong&gt;「반사」는 복사의 한 갈래일 뿐&lt;/strong&gt; 따로 세지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대류 · 전도 · 복사 · 증발&lt;/u&gt; 넷.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;열교환의 방법과 온열조건&lt;/strong&gt;&lt;br&gt;$S = M - E \pm R \pm C - W$라는 열균형 방정식에서 &lt;strong&gt;증발(E) · 복사(R) · 대류(C)&lt;/strong&gt;가 나온다. &lt;strong&gt;「반사」는 복사의 한 갈래일 뿐&lt;/strong&gt; 따로 세지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대류 · 전도 · 복사 · 증발&lt;/u&gt; 넷.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5841,17 +5841,17 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>정상사상은 &lt;strong&gt;좁고 구체적으로&lt;/strong&gt; 잡아야 한다. &lt;strong&gt;광범위하게 잡으면 나무가 걷잡을 수 없이 커져&lt;/strong&gt; 분석이 되지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FT 작성의 유의점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;유의점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분석 대상 시스템을 완전히 이해할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정상사상을 구체적이고 명확하게 정의할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「광범위하게」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정상사상과 기본사상의 관계를 논리게이트로 그릴 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;해석·평가에 앞서 불 대수로 FT 를 간소화할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;같은 수준(level)의 사상끼리 나란히 놓을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>정상사상은 &lt;strong&gt;좁고 구체적으로&lt;/strong&gt; 잡아야 한다. &lt;strong&gt;광범위하게 잡으면 나무가 걷잡을 수 없이 커져&lt;/strong&gt; 분석이 되지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FT 작성의 유의점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;유의점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분석 대상 시스템을 완전히 이해할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정상사상을 구체적이고 명확하게 정의할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「광범위하게」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정상사상과 기본사상의 관계를 논리게이트로 그릴 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;해석·평가에 앞서 불 대수로 FT를 간소화할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;같은 수준(level)의 사상끼리 나란히 놓을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① 해석·평가 전에 FT 를 간소화하는 것은 맞다.&lt;br&gt;② 정상사상과 기본사상의 관계를 논리게이트로 그리는 것도 맞다.&lt;br&gt;③ 분석 대상 시스템을 완전히 이해해야 하는 것도 맞다.</t>
+          <t>① 해석·평가 전에 FT를 간소화하는 것은 맞다.&lt;br&gt;② 정상사상과 기본사상의 관계를 논리게이트로 그리는 것도 맞다.&lt;br&gt;③ 분석 대상 시스템을 완전히 이해해야 하는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FT 의 작성방법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정상사상이 넓으면 가지가 끝없이 벌어진다&lt;/strong&gt; — &lt;strong&gt;「사고가 난다」가 아니라 「A 밸브에서 가스가 샌다」처럼 좁혀야&lt;/strong&gt; 나무가 그려진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정상사상은 구체적으로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FT의 작성방법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정상사상이 넓으면 가지가 끝없이 벌어진다&lt;/strong&gt; — &lt;strong&gt;「사고가 난다」가 아니라 「A 밸브에서 가스가 샌다」처럼 좁혀야&lt;/strong&gt; 나무가 그려진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정상사상은 구체적으로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>② FMEA 는 부품의 고장 형태와 영향을 보는 정성적 기법이다.&lt;br&gt;③ CA 는 치명도 분석이다.&lt;br&gt;④ FMECA 는 FMEA 와 CA 를 합친 것이다.</t>
+          <t>② FMEA는 부품의 고장 형태와 영향을 보는 정성적 기법이다.&lt;br&gt;③ CA는 치명도 분석이다.&lt;br&gt;④ FMECA는 FMEA와 CA를 합친 것이다.</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;점멸융합주파수(CFF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;밝고 또렷할수록 깜박임을 잘 구별&lt;/strong&gt; 하므로 CFF 가 높다. &lt;strong&gt;어둡거나(암조응) 지치면(피로) 내려간다&lt;/strong&gt;. &lt;strong&gt;「피로하면 내려간다」&lt;/strong&gt; 하나만 잡아도 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;피로하면 CFF 가 내려간다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;점멸융합주파수(CFF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;밝고 또렷할수록 깜박임을 잘 구별&lt;/strong&gt;하므로 CFF가 높다. &lt;strong&gt;어둡거나(암조응) 지치면(피로) 내려간다&lt;/strong&gt;. &lt;strong&gt;「피로하면 내려간다」&lt;/strong&gt; 하나만 잡아도 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;피로하면 CFF가 내려간다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6486,17 +6486,17 @@
       </c>
       <c r="AG42" s="32" t="inlineStr">
         <is>
-          <t>$H = \log_{2} N = \log_{2} 4 = 2$ [bit] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;선택지 수와 정보량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;선택지 수 N&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정보량 H&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;동전 던지기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;16&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H = \log_{2} N = \log_{2} 4 = 2$ [bit]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;선택지 수와 정보량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;선택지 수 N&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정보량 H&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;동전 던지기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;16&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [bit]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>① 1 [bit] 는 선택지가 2개일 때다.&lt;br&gt;③ 3 [bit] 는 8개일 때다.&lt;br&gt;④ 4 [bit] 는 16개일 때다.</t>
+          <t>① 1 [bit]는 선택지가 2개일 때다.&lt;br&gt;③ 3 [bit]는 8개일 때다.&lt;br&gt;④ 4 [bit]는 16개일 때다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정보량(information)&lt;/strong&gt;&lt;br&gt;$H = \log_{2} N$ 이다 — &lt;strong&gt;「몇 번 반으로 갈라야 하나」&lt;/strong&gt;를 세는 셈이다. &lt;strong&gt;4개를 두 번 반으로 가르면 하나가 남으므로 2 [bit]&lt;/strong&gt;다. &lt;strong&gt;확률이 다르면 &lt;/strong&gt;$H = \sum p_{i} \log_{2} ( 1 / p_{i} )$로 셈한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = \log_{2} N$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정보량(information)&lt;/strong&gt;&lt;br&gt;$H = \log_{2} N$이다 — &lt;strong&gt;「몇 번 반으로 갈라야 하나」&lt;/strong&gt;를 세는 셈이다. &lt;strong&gt;4개를 두 번 반으로 가르면 하나가 남으므로 2 [bit]&lt;/strong&gt;다. &lt;strong&gt;확률이 다르면 &lt;/strong&gt;$H = \sum p_{i} \log_{2} ( 1 / p_{i} )$로 셈한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = \log_{2} N$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AI44" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;셰이퍼의 위험요인&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셰이퍼는 램이 앞뒤로 왕복&lt;/strong&gt; 하며 깎는 기계다 — &lt;strong&gt;회전이 아니라 왕복&lt;/strong&gt;이므로 &lt;strong&gt;회전축·척에 딸린 위험은 나오지 않는다&lt;/strong&gt;. &lt;strong&gt;램 뒤쪽에 사람이 서지 않게 울을 치는&lt;/strong&gt; 것이 핵심 방호다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;척-핸들은 선반&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;셰이퍼의 위험요인&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셰이퍼는 램이 앞뒤로 왕복&lt;/strong&gt;하며 깎는 기계다 — &lt;strong&gt;회전이 아니라 왕복&lt;/strong&gt;이므로 &lt;strong&gt;회전축·척에 딸린 위험은 나오지 않는다&lt;/strong&gt;. &lt;strong&gt;램 뒤쪽에 사람이 서지 않게 울을 치는&lt;/strong&gt; 것이 핵심 방호다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;척-핸들은 선반&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="U46" s="32" t="inlineStr">
         <is>
-          <t>다음 중 프레스기계의 위험을 방지하기 위한 본질적 안전(no-hand in die 방식) 가 아닌 것은?</t>
+          <t>다음 중 프레스기계의 위험을 방지하기 위한 본질적 안전(no-hand in die 방식)가 아닌 것은?</t>
         </is>
       </c>
       <c r="V46" s="32" t="inlineStr"/>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AG46" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;수인식&lt;/strong&gt;은 &lt;strong&gt;손을 넣되 위험할 때 끌어내는&lt;/strong&gt; 장치다. &lt;strong&gt;no-hand in die 가 아니라 hand in die&lt;/strong&gt; 쪽이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스의 방호 — 손을 넣느냐로 가른다&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;no-hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전금형 · 금형의 안전 울 · 전용프레스 · 자동송급배출장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 아예 들어가지 않는다&lt;/u&gt; — 본질적 안전화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 들어가므로 방호장치로 막는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;수인식&lt;/strong&gt;은 &lt;strong&gt;손을 넣되 위험할 때 끌어내는&lt;/strong&gt; 장치다. &lt;strong&gt;no-hand in die가 아니라 hand in die&lt;/strong&gt; 쪽이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스의 방호 — 손을 넣느냐로 가른다&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;no-hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전금형 · 금형의 안전 울 · 전용프레스 · 자동송급배출장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 아예 들어가지 않는다&lt;/u&gt; — 본질적 안전화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 들어가므로 방호장치로 막는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH46" s="32" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AI47" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정(chisel) 작업의 안전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;끊어지기 직전이 가장 위험&lt;/strong&gt; 하다 — &lt;strong&gt;마지막 한 번의 세기가 조각의 속도&lt;/strong&gt;를 정한다. &lt;strong&gt;처음엔 약하게, 가운데는 세게, 마칠 때는 다시 약하게&lt;/strong&gt;가 순서다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;마칠 무렵엔 약하게&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정(chisel) 작업의 안전&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;끊어지기 직전이 가장 위험&lt;/strong&gt;하다 — &lt;strong&gt;마지막 한 번의 세기가 조각의 속도&lt;/strong&gt;를 정한다. &lt;strong&gt;처음엔 약하게, 가운데는 세게, 마칠 때는 다시 약하게&lt;/strong&gt;가 순서다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;마칠 무렵엔 약하게&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7647,17 +7647,17 @@
       </c>
       <c r="AG51" s="32" t="inlineStr">
         <is>
-          <t>$\dfrac{25}{4} = 6.25$ [kg/mm²] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율과 허용응력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = \dfrac{\text{극한강도} ( \text{인장강도} )}{\text{허용응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;허용응력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{극한강도}}{\text{안전율}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율의 다른 꼴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{파단하중}}{\text{안전하중}}$, $\dfrac{\text{파괴하중}}{\text{최대사용하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\dfrac{25}{4} = 6.25$ [kg/mm²]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율과 허용응력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = \dfrac{\text{극한강도} ( \text{인장강도} )}{\text{허용응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;허용응력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{극한강도}}{\text{안전율}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율의 다른 꼴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{파단하중}}{\text{안전하중}}$, $\dfrac{\text{파괴하중}}{\text{최대사용하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH51" s="32" t="inlineStr">
         <is>
-          <t>① 4.25 는 계산과 맞지 않는다.&lt;br&gt;③ 8.25 도 그렇다.&lt;br&gt;④ 10.25 도 그렇다.</t>
+          <t>① 4.25는 계산과 맞지 않는다.&lt;br&gt;③ 8.25 도 그렇다.&lt;br&gt;④ 10.25 도 그렇다.</t>
         </is>
       </c>
       <c r="AI51" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전율(안전계수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전율은 「몇 배로 버티게 해 두었나」&lt;/strong&gt;다 — &lt;strong&gt;클수록 안전하지만 재료가 낭비&lt;/strong&gt; 된다. &lt;strong&gt;허용응력은 그 배수만큼 낮춰 놓은 값&lt;/strong&gt;이므로 나눗셈이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;허용응력 = 인장강도 ÷ 안전율&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전율(안전계수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전율은 「몇 배로 버티게 해 두었나」&lt;/strong&gt;다 — &lt;strong&gt;클수록 안전하지만 재료가 낭비&lt;/strong&gt;된다. &lt;strong&gt;허용응력은 그 배수만큼 낮춰 놓은 값&lt;/strong&gt;이므로 나눗셈이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;허용응력 = 인장강도 ÷ 안전율&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7905,17 +7905,17 @@
       </c>
       <c r="AG53" s="32" t="inlineStr">
         <is>
-          <t>$D_{m} = 1 {,} 600 \times T_{m} = 1 {,} 600 \times 0.15 = 240$ [mm] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방호장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D_{m} = 1 {,} 600 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · $T_{m}$ 은 누름부터 하사점까지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손이 떨어진 뒤 급정지까지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빛을 가린 뒤 급정지까지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식·수인식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;행정길이 40 [mm] 이상에서 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$D_{m} = 1 {,} 600 \times T_{m} = 1 {,} 600 \times 0.15 = 240$ [mm]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방호장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D_{m} = 1 {,} 600 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · $T_{m}$은 누름부터 하사점까지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손이 떨어진 뒤 급정지까지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;빛을 가린 뒤 급정지까지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식·수인식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;행정길이 40 [mm] 이상에서 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>① 150 [mm] 는 계산과 맞지 않는다.&lt;br&gt;② 220 [mm] 도 그렇다.&lt;br&gt;④ 300 [mm] 도 그렇다.</t>
+          <t>① 150 [mm]는 계산과 맞지 않는다.&lt;br&gt;② 220 [mm] 도 그렇다.&lt;br&gt;④ 300 [mm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1,600 [mm/s] 는 사람 손이 뻗는 속도&lt;/strong&gt;로 잡은 값이다. &lt;strong&gt;「그 시간 동안 손이 갈 수 있는 거리만큼 떼어 놓는다」&lt;/strong&gt;는 것이 모든 안전거리 식의 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D_{m} = 1 {,} 600 T_{m}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수기동식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1,600 [mm/s]는 사람 손이 뻗는 속도&lt;/strong&gt;로 잡은 값이다. &lt;strong&gt;「그 시간 동안 손이 갈 수 있는 거리만큼 떼어 놓는다」&lt;/strong&gt;는 것이 모든 안전거리 식의 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $D_{m} = 1 {,} 600 T_{m}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8277,13 +8277,13 @@
       <c r="AA56" s="32" t="inlineStr"/>
       <c r="AB56" s="32" t="inlineStr">
         <is>
-          <t>수봉배기관은 안전기의 압력을 2.5kg/cm2 에 도달하기 전에 배기시킬 수 있는 능력을 갖추어야 한다.</t>
+          <t>수봉배기관은 안전기의 압력을 2.5kg/cm2에 도달하기 전에 배기시킬 수 있는 능력을 갖추어야 한다.</t>
         </is>
       </c>
       <c r="AC56" s="32" t="inlineStr"/>
       <c r="AD56" s="32" t="inlineStr">
         <is>
-          <t>파열판은 안전기 내의 압력이 50kg/cm2 에 도달하기 전에 파열되어야 한다.</t>
+          <t>파열판은 안전기 내의 압력이 50kg/cm2에 도달하기 전에 파열되어야 한다.</t>
         </is>
       </c>
       <c r="AE56" s="32" t="inlineStr"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="AH56" s="32" t="inlineStr">
         <is>
-          <t>② 유효수주는 20 [mm] 미만이 아니라 25 [mm] 이상이다.&lt;br&gt;③ 2.5 [kg/cm²] 는 저압용 수봉식의 배기 기준으로 지나치게 높다.&lt;br&gt;④ 파열판은 중압용 안전기의 요건이며 50 [kg/cm²] 는 지나치게 높다.</t>
+          <t>② 유효수주는 20 [mm] 미만이 아니라 25 [mm] 이상이다.&lt;br&gt;③ 2.5 [kg/cm²]는 저압용 수봉식의 배기 기준으로 지나치게 높다.&lt;br&gt;④ 파열판은 중압용 안전기의 요건이며 50 [kg/cm²]는 지나치게 높다.</t>
         </is>
       </c>
       <c r="AI56" s="32" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="AH58" s="32" t="inlineStr">
         <is>
-          <t>① 10,000 [Hz] 는 아직 들리는 소리다.&lt;br&gt;③ 50,000 [Hz] 는 초음파이기는 하나 경계값이 아니다.&lt;br&gt;④ 100,000 [Hz] 도 그렇다.</t>
+          <t>① 10,000 [Hz]는 아직 들리는 소리다.&lt;br&gt;③ 50,000 [Hz]는 초음파이기는 하나 경계값이 아니다.&lt;br&gt;④ 100,000 [Hz] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;초음파와 가청주파수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가청 범위 20 ~ 20,000 [Hz]&lt;/strong&gt;라는 두 숫자가 &lt;strong&gt;아래로는 초저주파, 위로는 초음파&lt;/strong&gt;의 경계를 함께 준다. &lt;strong&gt;소음성 난청이 4,000 [Hz] 에서 먼저 온다&lt;/strong&gt;는 것도 같이 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;초음파는 20,000 [Hz] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;초음파와 가청주파수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가청 범위 20 ~ 20,000 [Hz]&lt;/strong&gt;라는 두 숫자가 &lt;strong&gt;아래로는 초저주파, 위로는 초음파&lt;/strong&gt;의 경계를 함께 준다. &lt;strong&gt;소음성 난청이 4,000 [Hz]에서 먼저 온다&lt;/strong&gt;는 것도 같이 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;초음파는 20,000 [Hz] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8808,17 +8808,17 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>$T = m ( g + a ) = 100 \times ( 10 + 2 ) = 1 {,} 200$ [N] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;권상·권하 시의 장력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장력&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;멈춰 있거나 등속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = \mathrm{mg}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위로 가속(권상)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = m ( g + a )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; — 장력이 는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아래로 가속(권하)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = m ( g - a )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;장력이 준다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$T = m ( g + a ) = 100 \times ( 10 + 2 ) = 1 {,} 200$ [N]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;권상·권하 시의 장력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장력&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;멈춰 있거나 등속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = \mathrm{mg}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위로 가속(권상)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = m ( g + a )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; — 장력이 는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아래로 가속(권하)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = m ( g - a )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;장력이 준다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 200 [N] 은 $\mathrm{ma}$ 만 셈한 값이다.&lt;br&gt;② 300 [N] 은 계산과 맞지 않는다.&lt;br&gt;④ 2,000 [N] 은 $2 \mathrm{mg}$ 로 잘못 셈한 값이다.</t>
+          <t>① 200 [N]은 $\mathrm{ma}$만 셈한 값이다.&lt;br&gt;② 300 [N]은 계산과 맞지 않는다.&lt;br&gt;④ 2,000 [N]은 $2 \mathrm{mg}$로 잘못 셈한 값이다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;와이어로프에 걸리는 장력&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;올리려면 무게를 이기고도 남는 힘&lt;/strong&gt;이 있어야 하므로 &lt;strong&gt;장력은 정하중보다 커진다&lt;/strong&gt;. &lt;strong&gt;정하중 1,000 [N] 에 가속분 200 [N] 을 더한&lt;/strong&gt; 것이 1,200 [N] 이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T = m ( g + a )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;와이어로프에 걸리는 장력&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;올리려면 무게를 이기고도 남는 힘&lt;/strong&gt;이 있어야 하므로 &lt;strong&gt;장력은 정하중보다 커진다&lt;/strong&gt;. &lt;strong&gt;정하중 1,000 [N]에 가속분 200 [N]을 더한&lt;/strong&gt; 것이 1,200 [N]이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T = m ( g + a )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AI61" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;프레스의 자동송급·배출장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「피더」는 넣고 「에젝터」는 뺀다&lt;/strong&gt; — 이름만으로 갈린다. &lt;strong&gt;자동송급·배출장치를 붙이면 손이 금형에 들어갈 일이 없어&lt;/strong&gt; no-hand in die 가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;스트리퍼는 금형 부품&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;프레스의 자동송급·배출장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「피더」는 넣고 「에젝터」는 뺀다&lt;/strong&gt; — 이름만으로 갈린다. &lt;strong&gt;자동송급·배출장치를 붙이면 손이 금형에 들어갈 일이 없어&lt;/strong&gt; no-hand in die가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;스트리퍼는 금형 부품&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9195,17 +9195,17 @@
       </c>
       <c r="AG63" s="32" t="inlineStr">
         <is>
-          <t>50 ~ 100 [mA] 는 &lt;strong&gt;심실세동을 일으켜 대단히 위험한&lt;/strong&gt; 구간이지 &lt;strong&gt;「순간으로 확실하게 사망」&lt;/strong&gt; 하는 구간이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통전전류의 크기와 영향 (60 [Hz], 성인 남자)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영향&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소감지전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;찌릿함을 느낀다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고통한계전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 ~ 8 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;참을 수 있는 한계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가수(이탈가능)전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 ~ 15 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;스스로 손을 뗄 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불수(이탈불능)전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 ~ 50 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육이 굳어 손을 뗄 수 없다&lt;/u&gt; · 호흡곤란&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ~ 100 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심장이 잔떨림 — 대단히 위험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>50 ~ 100 [mA]는 &lt;strong&gt;심실세동을 일으켜 대단히 위험한&lt;/strong&gt; 구간이지 &lt;strong&gt;「순간으로 확실하게 사망」&lt;/strong&gt;하는 구간이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통전전류의 크기와 영향 (60 [Hz], 성인 남자)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영향&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최소감지전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;찌릿함을 느낀다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고통한계전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 ~ 8 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;참을 수 있는 한계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가수(이탈가능)전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 ~ 15 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;스스로 손을 뗄 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불수(이탈불능)전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 ~ 50 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육이 굳어 손을 뗄 수 없다&lt;/u&gt; · 호흡곤란&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ~ 100 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심장이 잔떨림 — 대단히 위험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 20 ~ 30 [mA] 에서 강한 근육수축과 호흡곤란이 오는 것은 맞다.&lt;br&gt;③ 1 ~ 8 [mA] 가 쇼크는 느끼되 기능에 영향이 없는 것도 맞다.&lt;br&gt;④ 15 ~ 20 [mA] 에서 감전부위 가까운 근육이 마비되는 것도 맞다.</t>
+          <t>① 20 ~ 30 [mA]에서 강한 근육수축과 호흡곤란이 오는 것은 맞다.&lt;br&gt;③ 1 ~ 8 [mA]가 쇼크는 느끼되 기능에 영향이 없는 것도 맞다.&lt;br&gt;④ 15 ~ 20 [mA]에서 감전부위 가까운 근육이 마비되는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;통전전류의 인체 영향&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「확실하게」 · 「반드시」 처럼 못을 박는 말이 붙으면 대개 틀린 보기&lt;/strong&gt;다. &lt;strong&gt;심실세동은 사망에 이를 수 있는 상태이지 즉사가 아니며, 3분 안에 제세동하면 살릴 수&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;50 ~ 100 [mA] 는 심실세동&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;통전전류의 인체 영향&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「확실하게」 · 「반드시」처럼 못을 박는 말이 붙으면 대개 틀린 보기&lt;/strong&gt;다. &lt;strong&gt;심실세동은 사망에 이를 수 있는 상태이지 즉사가 아니며, 3분 안에 제세동하면 살릴 수&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;50 ~ 100 [mA]는 심실세동&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AG64" s="32" t="inlineStr">
         <is>
-          <t>맨몸으로 잡으면 &lt;strong&gt;구조자까지 감전&lt;/strong&gt; 된다. &lt;strong&gt;전원을 끊거나 절연물로 떼어내야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전자 구출의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;할 일&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감전 상황을 판단한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;충전부에 닿아 있는지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 먼저 할 일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊을 수 없으면 절연물로 떼어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마른 막대 · 고무장갑 · 고무장화&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구조자도 보호구를 갖춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;의식·호흡·맥박을 확인하고 심폐소생술&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>맨몸으로 잡으면 &lt;strong&gt;구조자까지 감전&lt;/strong&gt;된다. &lt;strong&gt;전원을 끊거나 절연물로 떼어내야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전자 구출의 순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;할 일&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감전 상황을 판단한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;충전부에 닿아 있는지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원을 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 먼저 할 일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊을 수 없으면 절연물로 떼어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마른 막대 · 고무장갑 · 고무장화&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구조자도 보호구를 갖춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;⑤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;의식·호흡·맥박을 확인하고 심폐소생술&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH64" s="32" t="inlineStr">
@@ -9457,17 +9457,17 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>지락회로는 $R_{2}$&lt;strong&gt; 와 &lt;/strong&gt;$R_{3}$&lt;strong&gt; 이 직렬&lt;/strong&gt;이다. $I = \dfrac{200}{10 + 30} = 5$ [A] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지락회로의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구할 것&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지락전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I_{g} = \dfrac{V}{R_{2} + R_{3}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 접지저항의 직렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기기 외함의 대지전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = I_{g} R_{3} = V \cdot \dfrac{R_{3}}{R_{2} + R_{3}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항이면 150 [V]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;외함전압을 낮추려면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R_{3}$&lt;u&gt; 를 작게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;접지저항을 낮춘다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>지락회로는 $R_{2}$&lt;strong&gt;와 &lt;/strong&gt;$R_{3}$&lt;strong&gt;이 직렬&lt;/strong&gt;이다. $I = \dfrac{200}{10 + 30} = 5$ [A]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지락회로의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구할 것&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지락전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I_{g} = \dfrac{V}{R_{2} + R_{3}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 접지저항의 직렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기기 외함의 대지전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = I_{g} R_{3} = V \cdot \dfrac{R_{3}}{R_{2} + R_{3}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항이면 150 [V]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;외함전압을 낮추려면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R_{3}$&lt;u&gt;를 작게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;접지저항을 낮춘다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
-          <t>② 10 [A] 는 저항 하나만으로 나눈 값이다.&lt;br&gt;③ 15 [A] 는 계산과 맞지 않는다.&lt;br&gt;④ 20 [A] 도 그렇다.</t>
+          <t>② 10 [A]는 저항 하나만으로 나눈 값이다.&lt;br&gt;③ 15 [A]는 계산과 맞지 않는다.&lt;br&gt;④ 20 [A] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지락전류와 외함 대지전압&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전류는 「변압기 → 상선 → 기기 → &lt;/strong&gt;$R_{3}$&lt;strong&gt; → 대지 → &lt;/strong&gt;$R_{2}$&lt;strong&gt; → 변압기」&lt;/strong&gt;로 한 바퀴 돈다 — &lt;strong&gt;한 줄이므로 직렬&lt;/strong&gt;이다. &lt;strong&gt;외함에 걸리는 전압은 &lt;/strong&gt;$R_{3}$&lt;strong&gt; 이 나누어 갖는 몫&lt;/strong&gt;이라 $R_{3}$&lt;strong&gt; 을 낮출수록 안전&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지락전류는 두 접지저항의 직렬&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;제2종·제3종 접지&lt;/u&gt;라는 종별 구분은 &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 없어지고 &lt;u&gt;계통접지·보호접지&lt;/u&gt;로 바뀌었다. 회로의 셈법은 그대로다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지락전류와 외함 대지전압&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전류는 「변압기 → 상선 → 기기 → &lt;/strong&gt;$R_{3}$&lt;strong&gt; → 대지 → &lt;/strong&gt;$R_{2}$&lt;strong&gt; → 변압기」&lt;/strong&gt;로 한 바퀴 돈다 — &lt;strong&gt;한 줄이므로 직렬&lt;/strong&gt;이다. &lt;strong&gt;외함에 걸리는 전압은 &lt;/strong&gt;$R_{3}$&lt;strong&gt;이 나누어 갖는 몫&lt;/strong&gt;이라 $R_{3}$&lt;strong&gt;을 낮출수록 안전&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지락전류는 두 접지저항의 직렬&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;제2종·제3종 접지&lt;/u&gt;라는 종별 구분은 &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 없어지고 &lt;u&gt;계통접지·보호접지&lt;/u&gt;로 바뀌었다. 회로의 셈법은 그대로다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9973,17 +9973,17 @@
       </c>
       <c r="AG69" s="32" t="inlineStr">
         <is>
-          <t>심실세동전류는 $I = \dfrac{165}{\sqrt{T}}$ [mA] 이므로 1초에서 165 [mA] 다. $W = I^{2} R T = ( 0.165 )^{2} \times 1 {,} 000 \times 1 \fallingdotseq 27.23$ [J] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;심실세동과 위험한계 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T 는 통전시간 [초]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 1,000 [Ω], T = 1초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;27.23 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 500 [Ω], T = 1초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13.6 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;자주 함께 나온다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>심실세동전류는 $I = \dfrac{165}{\sqrt{T}}$ [mA]이므로 1초에서 165 [mA]다. $W = I^{2} R T = ( 0.165 )^{2} \times 1 {,} 000 \times 1 \fallingdotseq 27.23$ [J]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;심실세동과 위험한계 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T는 통전시간 [초]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 1,000 [Ω], T = 1초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;27.23 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 500 [Ω], T = 1초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13.6 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;자주 함께 나온다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 17.33 [J] 는 계산과 맞지 않는다.&lt;br&gt;③ 37.33 [J] 도 그렇다.&lt;br&gt;④ 47.23 [J] 도 그렇다.</t>
+          <t>① 17.33 [J]는 계산과 맞지 않는다.&lt;br&gt;③ 37.33 [J] 도 그렇다.&lt;br&gt;④ 47.23 [J] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험한계 에너지&lt;/strong&gt;&lt;br&gt;$W = I^{2} R T$ 에서 $I$ 에 $165 / \sqrt{T}$ 를 넣으면 $T$ 가 약분되어 $W = ( 0.165 )^{2} R$만 남는다 — &lt;strong&gt;통전시간과 무관하게 저항만으로 정해진다&lt;/strong&gt;. &lt;strong&gt;R = 1,000 이면 27.23, R = 500 이면 13.6&lt;/strong&gt; 두 값만 외워 두면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Ω] 이면 27.23 [J]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험한계 에너지&lt;/strong&gt;&lt;br&gt;$W = I^{2} R T$에서 $I$에 $165 / \sqrt{T}$를 넣으면 $T$가 약분되어 $W = ( 0.165 )^{2} R$만 남는다 — &lt;strong&gt;통전시간과 무관하게 저항만으로 정해진다&lt;/strong&gt;. &lt;strong&gt;R = 1,000 이면 27.23, R = 500 이면 13.6&lt;/strong&gt; 두 값만 외워 두면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Ω] 이면 27.23 [J]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10094,17 +10094,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지붕과 한 면의 벽만 있어 바깥 공기가 드나드는 건축물&lt;/strong&gt;은 환기가 충분한 장소로 본다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;환기가 충분한 장소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보는 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발하한계의 25% 를 넘겨 쌓이지 않을 만큼의 환기량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「50%」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지붕과 한 면의 벽만 있는 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바깥 공기 흐름을 막지 않는 구조&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강제환기방식으로 옥외와 같은 정도의 환기가 보장되는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「자연 순환방식」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계산으로 폭발하한계의 15% 를 넘지 않음이 보장되는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「35%」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;지붕과 한 면의 벽만 있어 바깥 공기가 드나드는 건축물&lt;/strong&gt;은 환기가 충분한 장소로 본다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;환기가 충분한 장소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보는 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발하한계의 25%를 넘겨 쌓이지 않을 만큼의 환기량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「50%」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지붕과 한 면의 벽만 있는 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바깥 공기 흐름을 막지 않는 구조&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강제환기방식으로 옥외와 같은 정도의 환기가 보장되는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「자연 순환방식」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계산으로 폭발하한계의 15%를 넘지 않음이 보장되는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「35%」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 폭발하한계의 50% 가 아니라 25% 다.&lt;br&gt;③ 자연 순환방식이 아니라 강제환기방식이다.&lt;br&gt;④ 35% 가 아니라 15% 다.</t>
+          <t>① 폭발하한계의 50%가 아니라 25%다.&lt;br&gt;③ 자연 순환방식이 아니라 강제환기방식이다.&lt;br&gt;④ 35%가 아니라 15%다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;환기가 충분한 장소&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;25% 와 15% 두 숫자&lt;/strong&gt;가 갈림길이다 — &lt;strong&gt;쌓이는 것을 막는 일반 기준이 25%, 계산으로 증명할 때가 15%&lt;/strong&gt;다. &lt;strong&gt;숫자를 부풀린 보기 셋을 걸러내면&lt;/strong&gt; 남는 것이 답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하한계의 25%, 계산은 15%&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;환기가 충분한 장소&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;25%와 15% 두 숫자&lt;/strong&gt;가 갈림길이다 — &lt;strong&gt;쌓이는 것을 막는 일반 기준이 25%, 계산으로 증명할 때가 15%&lt;/strong&gt;다. &lt;strong&gt;숫자를 부풀린 보기 셋을 걸러내면&lt;/strong&gt; 남는 것이 답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하한계의 25%, 계산은 15%&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10357,12 +10357,12 @@
       </c>
       <c r="AH72" s="32" t="inlineStr">
         <is>
-          <t>② G2 는 300 [℃] 초과 450 [℃] 이하다.&lt;br&gt;③ G3 는 200 [℃] 초과 300 [℃] 이하다.&lt;br&gt;④ G4 는 135 [℃] 초과 200 [℃] 이하다.</t>
+          <t>② G2는 300 [℃] 초과 450 [℃] 이하다.&lt;br&gt;③ G3는 200 [℃] 초과 300 [℃] 이하다.&lt;br&gt;④ G4는 135 [℃] 초과 200 [℃] 이하다.</t>
         </is>
       </c>
       <c r="AI72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;발화도 등급과 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;발화도 G1 ~ G6 와 기기의 온도등급 T1 ~ T6 는 숫자가 같은 칸끼리 짝&lt;/strong&gt;이다 — &lt;strong&gt;450 / 300 / 200 / 135 / 100 / 85&lt;/strong&gt;이라는 여섯 숫자 하나로 두 표를 다 쓴다. &lt;strong&gt;기기의 최고표면온도가 가스의 발화점보다 낮아야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;450 · 300 · 200 · 135 · 100 · 85&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;발화도 등급과 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;발화도 G1 ~ G6와 기기의 온도등급 T1 ~ T6는 숫자가 같은 칸끼리 짝&lt;/strong&gt;이다 — &lt;strong&gt;450 / 300 / 200 / 135 / 100 / 85&lt;/strong&gt;이라는 여섯 숫자 하나로 두 표를 다 쓴다. &lt;strong&gt;기기의 최고표면온도가 가스의 발화점보다 낮아야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;450 · 300 · 200 · 135 · 100 · 85&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10486,12 +10486,12 @@
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>② 300 [℃] 초과 450 [℃] 이하는 T3 가 아니라 T1 이다.&lt;br&gt;③ 450 [℃] 를 넘는 등급은 없다.&lt;br&gt;④ 600 [℃] 를 넘는 등급도 없다.</t>
+          <t>② 300 [℃] 초과 450 [℃] 이하는 T3가 아니라 T1이다.&lt;br&gt;③ 450 [℃]를 넘는 등급은 없다.&lt;br&gt;④ 600 [℃]를 넘는 등급도 없다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭기기의 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;온도등급은 450 [℃] 에서 시작해 85 [℃] 까지 내려간다&lt;/strong&gt; — &lt;strong&gt;450 을 넘는 등급은 아예 없으므로&lt;/strong&gt; ③④는 보자마자 걸러진다. &lt;strong&gt;숫자가 클수록 표면이 차갑고 엄격&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T2 는 200 ~ 300 [℃]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭기기의 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;온도등급은 450 [℃]에서 시작해 85 [℃]까지 내려간다&lt;/strong&gt; — &lt;strong&gt;450을 넘는 등급은 아예 없으므로&lt;/strong&gt; ③④는 보자마자 걸러진다. &lt;strong&gt;숫자가 클수록 표면이 차갑고 엄격&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T2는 200 ~ 300 [℃]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10610,17 +10610,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$W = \dfrac{1}{2} C V^{2}$ 이므로 $V = \sqrt{\dfrac{2 W}{C}} = \sqrt{\dfrac{2 \times 1.15 \times 10^{-3}}{100 \times 10^{-12}}} \fallingdotseq 4 {,} 800$ [V] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방전에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} Q V$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;[J]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \sqrt{\dfrac{2 W}{C}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [pF] = 10⁻¹² [F], 1 [mJ] = 10⁻³ [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단위 환산이 갈림길&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$W = \dfrac{1}{2} C V^{2}$이므로 $V = \sqrt{\dfrac{2 W}{C}} = \sqrt{\dfrac{2 \times 1.15 \times 10^{-3}}{100 \times 10^{-12}}} \fallingdotseq 4 {,} 800$ [V]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방전에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} Q V$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;[J]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \sqrt{\dfrac{2 W}{C}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [pF] = 10⁻¹² [F], 1 [mJ] = 10⁻³ [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단위 환산이 갈림길&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 1,150 [V] 는 계산과 맞지 않는다.&lt;br&gt;② 2,150 [V] 도 그렇다.&lt;br&gt;③ 3,800 [V] 도 그렇다.</t>
+          <t>① 1,150 [V]는 계산과 맞지 않는다.&lt;br&gt;② 2,150 [V] 도 그렇다.&lt;br&gt;③ 3,800 [V] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;방전에너지가 최소발화에너지보다 작아야 안전&lt;/strong&gt; 하다는 것이 이 셈의 바탕이다. &lt;strong&gt;pF 과 mJ 의 지수를 맞추는 데서 대부분 틀린다&lt;/strong&gt; — &lt;strong&gt;10⁻³ 과 10⁻¹² 를 나누면 10⁹&lt;/strong&gt;이 남는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;방전에너지가 최소발화에너지보다 작아야 안전&lt;/strong&gt; 하다는 것이 이 셈의 바탕이다. &lt;strong&gt;pF과 mJ의 지수를 맞추는 데서 대부분 틀린다&lt;/strong&gt; — &lt;strong&gt;10⁻³ 과 10⁻¹² 를 나누면 10⁹&lt;/strong&gt;이 남는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AG76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;대전방지용 구두&lt;/strong&gt;는 &lt;strong&gt;정전기를 대지로 흘려보내는&lt;/strong&gt; 신이다. &lt;strong&gt;활선작업에서는 오히려 위험&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;활선작업의 보호구&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보호구&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연용 안전모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;머리의 감전과 충격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연장갑(고무장갑)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손의 감전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연화·절연장화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;발쪽 통전경로를 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연복·절연 어깨받이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전방지용 구두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정전기를 대지로 흘린다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;활선작업에는 맞지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;대전방지용 구두&lt;/strong&gt;는 &lt;strong&gt;정전기를 대지로 흘려보내는&lt;/strong&gt; 신이다. &lt;strong&gt;활선작업에서는 오히려 위험&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;활선작업의 보호구&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보호구&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연용 안전모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;머리의 감전과 충격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연장갑(고무장갑)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손의 감전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연화·절연장화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;발쪽 통전경로를 끊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연복·절연 어깨받이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대전방지용 구두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정전기를 대지로 흘린다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;활선작업에는 맞지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH76" s="32" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AI76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;활선작업용 보호구&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;활선작업은 전기를 「끊어야」 하고 정전기 대책은 전기를 「흘려야」&lt;/strong&gt; 한다 — &lt;strong&gt;정반대&lt;/strong&gt;다. &lt;strong&gt;대전방지화는 저항이 낮아 감전경로를 만들어 준다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대전방지화는 정전기용&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;활선작업용 보호구&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;활선작업은 전기를 「끊어야」 하고 정전기 대책은 전기를 「흘려야」&lt;/strong&gt;한다 — &lt;strong&gt;정반대&lt;/strong&gt;다. &lt;strong&gt;대전방지화는 저항이 낮아 감전경로를 만들어 준다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대전방지화는 정전기용&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="AG77" s="32" t="inlineStr">
         <is>
-          <t>닿은 것은 &lt;strong&gt;동력용 COS&lt;/strong&gt;이고, &lt;strong&gt;전등용 1차측은 이미 개방&lt;/strong&gt; 되어 있었다. &lt;strong&gt;전등용 2차측&lt;/strong&gt;은 이 사고와 관계가 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이 사고의 원인&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인입구 개폐기(LS)를 열지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위쪽 전원이 살아 있었다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동력용 변압기 COS 를 열지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;닿은 바로 그 충전부&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전장구를 쓰지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;절연장갑 미착용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전등용 변압기 2차측 COS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고와 관계가 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>닿은 것은 &lt;strong&gt;동력용 COS&lt;/strong&gt;이고, &lt;strong&gt;전등용 1차측은 이미 개방&lt;/strong&gt;되어 있었다. &lt;strong&gt;전등용 2차측&lt;/strong&gt;은 이 사고와 관계가 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이 사고의 원인&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인입구 개폐기(LS)를 열지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위쪽 전원이 살아 있었다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동력용 변압기 COS를 열지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;닿은 바로 그 충전부&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전장구를 쓰지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;절연장갑 미착용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전등용 변압기 2차측 COS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고와 관계가 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>① 인입구 개폐기를 열지 않은 것은 사고 원인이다.&lt;br&gt;② 동력용 변압기 COS 를 열지 않은 것도 그렇다.&lt;br&gt;③ 안전장구를 쓰지 않은 것도 그렇다.</t>
+          <t>① 인입구 개폐기를 열지 않은 것은 사고 원인이다.&lt;br&gt;② 동력용 변압기 COS를 열지 않은 것도 그렇다.&lt;br&gt;③ 안전장구를 쓰지 않은 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;흙 자체는 전기가 잘 통하지 않는다&lt;/strong&gt;. &lt;strong&gt;단면적이 사실상 무한히 넓어&lt;/strong&gt; 전체 저항이 0 에 가까워지는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;대지를 접지로 쓰는 까닭&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지는 넓어 전류가 지날 길이 무수히 많다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \rho \dfrac{l}{A}$ 에서 &lt;u&gt;A 가 무한대&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그래서 전체 저항이 0 에 가깝다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 성분(규소·알루미나·철분)은 까닭이 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙 자체는 저항이 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접지저항의 대부분은 전극 바로 둘레에서 생긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전극을 깊고 넓게 · 접지저항 저감제&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;흙 자체는 전기가 잘 통하지 않는다&lt;/strong&gt;. &lt;strong&gt;단면적이 사실상 무한히 넓어&lt;/strong&gt; 전체 저항이 0에 가까워지는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;대지를 접지로 쓰는 까닭&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지는 넓어 전류가 지날 길이 무수히 많다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \rho \dfrac{l}{A}$에서 &lt;u&gt;A가 무한대&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그래서 전체 저항이 0에 가깝다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 성분(규소·알루미나·철분)은 까닭이 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙 자체는 저항이 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접지저항의 대부분은 전극 바로 둘레에서 생긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전극을 깊고 넓게 · 접지저항 저감제&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="AI79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;접지의 원리&lt;/strong&gt;&lt;br&gt;$R = \rho \dfrac{l}{A}$ 에서 &lt;strong&gt;대지는 A 가 사실상 무한대&lt;/strong&gt;라 &lt;strong&gt;저항률 &lt;/strong&gt;$\rho$&lt;strong&gt; 가 커도 전체 저항이 작아진다&lt;/strong&gt;. &lt;strong&gt;저항의 대부분은 전극 가까운 좁은 곳에서 생기므로&lt;/strong&gt; &lt;strong&gt;전극을 깊고 넓게 묻는 것&lt;/strong&gt;이 효과가 크다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;넓어서 저항이 0 에 가깝다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;접지의 원리&lt;/strong&gt;&lt;br&gt;$R = \rho \dfrac{l}{A}$에서 &lt;strong&gt;대지는 A가 사실상 무한대&lt;/strong&gt;라 &lt;strong&gt;저항률 &lt;/strong&gt;$\rho$&lt;strong&gt;가 커도 전체 저항이 작아진다&lt;/strong&gt;. &lt;strong&gt;저항의 대부분은 전극 가까운 좁은 곳에서 생기므로&lt;/strong&gt; &lt;strong&gt;전극을 깊고 넓게 묻는 것&lt;/strong&gt;이 효과가 크다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;넓어서 저항이 0에 가깝다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11776,12 +11776,12 @@
       </c>
       <c r="AH83" s="32" t="inlineStr">
         <is>
-          <t>② 메탄은 약 0.28 [mJ] 로 넷 가운데 가장 크다.&lt;br&gt;③ 에탄은 약 0.24 [mJ] 다.&lt;br&gt;④ 프로판은 약 0.26 [mJ] 다.</t>
+          <t>② 메탄은 약 0.28 [mJ]로 넷 가운데 가장 크다.&lt;br&gt;③ 에탄은 약 0.24 [mJ]다.&lt;br&gt;④ 프로판은 약 0.26 [mJ]다.</t>
         </is>
       </c>
       <c r="AI83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작을수록 불붙기 쉽다&lt;/strong&gt;. &lt;strong&gt;수소·아세틸렌처럼 분자가 작고 연소속도가 빠른 것&lt;/strong&gt;이 작다. &lt;strong&gt;MIE 는 압력이 높을수록, 농도가 화학양론농도에 가까울수록, 산소농도가 높을수록 작아진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수소가 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소발화에너지(MIE)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작을수록 불붙기 쉽다&lt;/strong&gt;. &lt;strong&gt;수소·아세틸렌처럼 분자가 작고 연소속도가 빠른 것&lt;/strong&gt;이 작다. &lt;strong&gt;MIE는 압력이 높을수록, 농도가 화학양론농도에 가까울수록, 산소농도가 높을수록 작아진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수소가 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12033,17 +12033,17 @@
       </c>
       <c r="AG85" s="32" t="inlineStr">
         <is>
-          <t>메탄은 $O_{2} = 2$ 이므로 $C_{\mathrm{st}} = 9.49$, $L = 5.2$ 이고, 부탄은 $O_{2} = 6.5$ 이므로 $C_{\mathrm{st}} = 3.13$, $L = 1.72$ 다. 르 샤틀리에 식으로 $\dfrac{100}{L} = \dfrac{70}{5.2} + \dfrac{30}{1.72} = 30.9$ 이므로 $L \fallingdotseq 3.2$ [vol%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합가스의 폭발범위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화학양론농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 O_{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$O_{2}$ 는 완전연소에 드는 산소 몰수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;존스(Jones) 하한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L \fallingdotseq 0.55 C_{\mathrm{st}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상한은 &lt;/u&gt;$3.50 C_{\mathrm{st}}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;르 샤틀리에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;섞인 기체의 폭발범위&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 몰수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄 2, 에탄 3.5, 프로판 5, 부탄 6.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>메탄은 $O_{2} = 2$이므로 $C_{\mathrm{st}} = 9.49$, $L = 5.2$이고, 부탄은 $O_{2} = 6.5$이므로 $C_{\mathrm{st}} = 3.13$, $L = 1.72$다. 르 샤틀리에 식으로 $\dfrac{100}{L} = \dfrac{70}{5.2} + \dfrac{30}{1.72} = 30.9$이므로 $L \fallingdotseq 3.2$ [vol%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합가스의 폭발범위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화학양론농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 O_{2}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$O_{2}$는 완전연소에 드는 산소 몰수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;존스(Jones) 하한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L \fallingdotseq 0.55 C_{\mathrm{st}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상한은 &lt;/u&gt;$3.50 C_{\mathrm{st}}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;르 샤틀리에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;섞인 기체의 폭발범위&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 몰수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄 2, 에탄 3.5, 프로판 5, 부탄 6.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>① 1.2 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 5.7 [vol%] 도 그렇다.&lt;br&gt;④ 7.7 [vol%] 도 그렇다.</t>
+          <t>① 1.2 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 5.7 [vol%] 도 그렇다.&lt;br&gt;④ 7.7 [vol%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에 식과 존스 식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;르 샤틀리에 식은 「역수의 가중평균」&lt;/strong&gt;이다 — &lt;strong&gt;하한이 낮은(잘 터지는) 성분이 결과를 끌어내린다&lt;/strong&gt;. &lt;strong&gt;부탄 30% 가 섞였는데도 값이 메탄 단독(5.2)보다 훨씬 낮아지는&lt;/strong&gt; 까닭이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에 식과 존스 식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;르 샤틀리에 식은 「역수의 가중평균」&lt;/strong&gt;이다 — &lt;strong&gt;하한이 낮은(잘 터지는) 성분이 결과를 끌어내린다&lt;/strong&gt;. &lt;strong&gt;부탄 30%가 섞였는데도 값이 메탄 단독(5.2)보다 훨씬 낮아지는&lt;/strong&gt; 까닭이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;알킬알루미늄의 소화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;알킬알루미늄은 공기에 닿기만 해도 스스로 타는(자연발화성) 데다 물과도 격렬히 반응&lt;/strong&gt; 한다 — &lt;strong&gt;물 · 이산화탄소 · 할론이 모두 막힌다&lt;/strong&gt;. 남는 것이 &lt;strong&gt;덮어 끄는 마른 모래 계열&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;알킬알루미늄은 팽창질석&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;알킬알루미늄의 소화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;알킬알루미늄은 공기에 닿기만 해도 스스로 타는(자연발화성) 데다 물과도 격렬히 반응&lt;/strong&gt;한다 — &lt;strong&gt;물 · 이산화탄소 · 할론이 모두 막힌다&lt;/strong&gt;. 남는 것이 &lt;strong&gt;덮어 끄는 마른 모래 계열&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;알킬알루미늄은 팽창질석&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12291,17 +12291,17 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>프로판은 $C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$ 이다. $\mathrm{MOC} = \mathrm{LFL} \times \dfrac{\text{산소 몰수}}{\text{연료 몰수}} = 2.2 \times 5 = 11$ [vol%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;최소산소농도(MOC)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{MOC} = \mathrm{LFL} \times \dfrac{O_{2} \text{몰수}}{\text{연료 몰수}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.2 × 5 = 11 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 × 2 = 10 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그 아래로 산소를 낮추면 타지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불활성화(퍼지)의 목표값&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>프로판은 $C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$이다. $\mathrm{MOC} = \mathrm{LFL} \times \dfrac{\text{산소 몰수}}{\text{연료 몰수}} = 2.2 \times 5 = 11$ [vol%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;최소산소농도(MOC)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{MOC} = \mathrm{LFL} \times \dfrac{O_{2} \text{몰수}}{\text{연료 몰수}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.2 × 5 = 11 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 × 2 = 10 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그 아래로 산소를 낮추면 타지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불활성화(퍼지)의 목표값&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
         <is>
-          <t>① 8 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 14 [vol%] 도 그렇다.&lt;br&gt;④ 16 [vol%] 도 그렇다.</t>
+          <t>① 8 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 14 [vol%] 도 그렇다.&lt;br&gt;④ 16 [vol%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MOC 는 「연료가 하한만큼 있을 때 그것을 태우는 데 드는 산소」&lt;/strong&gt;다. &lt;strong&gt;질소·이산화탄소를 넣어 산소를 MOC 아래로 낮추는 것이 불활성화&lt;/strong&gt;이며, &lt;strong&gt;실제로는 여기서 4 [vol%] 쯤 더 낮춰&lt;/strong&gt; 잡는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MOC} = \mathrm{LFL} \times O_{2}$ 몰수.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;MOC는 「연료가 하한만큼 있을 때 그것을 태우는 데 드는 산소」&lt;/strong&gt;다. &lt;strong&gt;질소·이산화탄소를 넣어 산소를 MOC 아래로 낮추는 것이 불활성화&lt;/strong&gt;이며, &lt;strong&gt;실제로는 여기서 4 [vol%] 쯤 더 낮춰&lt;/strong&gt; 잡는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $\mathrm{MOC} = \mathrm{LFL} \times O_{2}$ 몰수.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12678,17 +12678,17 @@
       </c>
       <c r="AG90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;알코올도 −OH 를 가진 물과 비슷한 물질&lt;/strong&gt;이라 알칼리금속과 반응한다. &lt;strong&gt;석유·등유·유동파라핀 속&lt;/strong&gt;에 저장한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;알칼리금속(Li, Na, K)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;성질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물과 반응해 수소를 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$2 \mathrm{Na} + 2 H_{2} O \rightarrow 2 \mathrm{NaOH} + H_{2}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;알코올과도 반응한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;알코올 속 저장은 안 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;석유 · 등유 · 유동파라핀 속&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Li 0.53, Na 0.97 — 둘 다 물보다 가볍다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겉모습&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;은백색의 무른 금속&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;알코올도 −OH를 가진 물과 비슷한 물질&lt;/strong&gt;이라 알칼리금속과 반응한다. &lt;strong&gt;석유·등유·유동파라핀 속&lt;/strong&gt;에 저장한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;알칼리금속(Li, Na, K)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;성질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물과 반응해 수소를 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$2 \mathrm{Na} + 2 H_{2} O \rightarrow 2 \mathrm{NaOH} + H_{2}$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;알코올과도 반응한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;알코올 속 저장은 안 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;석유 · 등유 · 유동파라핀 속&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Li 0.53, Na 0.97 — 둘 다 물보다 가볍다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겉모습&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;은백색의 무른 금속&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>② 두 금속이 물과 반응해 수소를 내는 것은 맞다.&lt;br&gt;③ Li 의 비중이 0.53 으로 물보다 작은 것도 맞다.&lt;br&gt;④ Na 가 은백색의 무른 금속인 것도 맞다.</t>
+          <t>② 두 금속이 물과 반응해 수소를 내는 것은 맞다.&lt;br&gt;③ Li의 비중이 0.53으로 물보다 작은 것도 맞다.&lt;br&gt;④ Na가 은백색의 무른 금속인 것도 맞다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;알칼리금속의 저장&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;알칼리금속은 「−OH 를 가진 것」과 모두 반응&lt;/strong&gt; 한다 — &lt;strong&gt;물도 알코올도 안 된다&lt;/strong&gt;. &lt;strong&gt;반응하지 않는 기름 속에 잠가&lt;/strong&gt; 공기와 습기를 끊는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;알칼리금속은 기름 속에&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;알칼리금속의 저장&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;알칼리금속은 「−OH를 가진 것」과 모두 반응&lt;/strong&gt;한다 — &lt;strong&gt;물도 알코올도 안 된다&lt;/strong&gt;. &lt;strong&gt;반응하지 않는 기름 속에 잠가&lt;/strong&gt; 공기와 습기를 끊는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;알칼리금속은 기름 속에&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="AI92" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자기반응성물질의 소화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기를 끊는 소화(질식)는 「산소를 밖에서 얻는 불」에만 듣는다&lt;/strong&gt; — &lt;strong&gt;제 안에 산소가 있으면 소용없다&lt;/strong&gt;. &lt;strong&gt;남는 방법은 물로 온도를 발화점 아래로 끌어내리는 냉각소화&lt;/strong&gt; 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자기반응성물질엔 다량 주수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자기반응성물질의 소화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기를 끊는 소화(질식)는 「산소를 밖에서 얻는 불」에만 듣는다&lt;/strong&gt; — &lt;strong&gt;제 안에 산소가 있으면 소용없다&lt;/strong&gt;. &lt;strong&gt;남는 방법은 물로 온도를 발화점 아래로 끌어내리는 냉각소화&lt;/strong&gt;뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자기반응성물질엔 다량 주수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13065,17 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 5} = 4.02$ 이므로 $\mathrm{LFL} = 0.55 \times 4.02 = 2.21$ 이고, $\mathrm{MOC} = 2.21 \times 5 \fallingdotseq 11.1$ [vol%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;존스 식으로 구하는 MOC&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 산소 몰수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;프로판은 5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 화학양론농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 5} = 4.02$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 폭발하한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.55 × 4.02 = 2.21 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;존스 식&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④ MOC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.21 × 5 = 11.1 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 5} = 4.02$이므로 $\mathrm{LFL} = 0.55 \times 4.02 = 2.21$이고, $\mathrm{MOC} = 2.21 \times 5 \fallingdotseq 11.1$ [vol%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;존스 식으로 구하는 MOC&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 산소 몰수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;프로판은 5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{3} H_{8} + 5 O_{2} \rightarrow 3 CO_{2} + 4 H_{2} O$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 화학양론농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 5} = 4.02$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 폭발하한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.55 × 4.02 = 2.21 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;존스 식&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④ MOC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.21 × 5 = 11.1 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① 8.1 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 15.1 [vol%] 도 그렇다.&lt;br&gt;④ 20.1 [vol%] 도 그렇다.</t>
+          <t>① 8.1 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 15.1 [vol%] 도 그렇다.&lt;br&gt;④ 20.1 [vol%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하한을 자료값 2.2 로 쓰든 존스 식으로 2.21 을 구하든 MOC 는 11 언저리&lt;/strong&gt;로 같다 — &lt;strong&gt;두 문항의 답이 어긋나지 않는&lt;/strong&gt; 까닭이다. &lt;strong&gt;단서에 「Jones 식」이 있으면 &lt;/strong&gt;$C_{\mathrm{st}}$&lt;strong&gt; 부터&lt;/strong&gt; 셈한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;프로판 MOC 는 11 [vol%]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하한을 자료값 2.2로 쓰든 존스 식으로 2.21을 구하든 MOC는 11 언저리&lt;/strong&gt;로 같다 — &lt;strong&gt;두 문항의 답이 어긋나지 않는&lt;/strong&gt; 까닭이다. &lt;strong&gt;단서에 「Jones 식」이 있으면 &lt;/strong&gt;$C_{\mathrm{st}}$&lt;strong&gt;부터&lt;/strong&gt; 셈한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;프로판 MOC는 11 [vol%]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AI94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;잠함병(감압병)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기의 78% 가 질소&lt;/strong&gt;이고 &lt;strong&gt;산소는 몸이 써 버리지만 질소는 그대로 녹아 있다&lt;/strong&gt; — &lt;strong&gt;압력이 갑자기 내려가면 사이다 뚜껑을 딴 것처럼 거품&lt;/strong&gt;이 된다. &lt;strong&gt;천천히 감압하는 것&lt;/strong&gt;이 예방이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;잠함병은 질소&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;잠함병(감압병)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기의 78%가 질소&lt;/strong&gt;이고 &lt;strong&gt;산소는 몸이 써 버리지만 질소는 그대로 녹아 있다&lt;/strong&gt; — &lt;strong&gt;압력이 갑자기 내려가면 사이다 뚜껑을 딴 것처럼 거품&lt;/strong&gt;이 된다. &lt;strong&gt;천천히 감압하는 것&lt;/strong&gt;이 예방이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;잠함병은 질소&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13452,17 +13452,17 @@
       </c>
       <c r="AG96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;물질 및 열수지&lt;/strong&gt;는 &lt;strong&gt;공정흐름도(PFD)&lt;/strong&gt;에 담는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PFD 와 P&amp;amp;ID&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공정흐름도(PFD)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공정배관계장도(P&amp;amp;ID)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공정의 큰 흐름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;배관과 계기까지 낱낱이&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;담는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물질수지 · 열수지 · 운전온도와 압력 · 주요 장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 배관의 호칭지름·재질·플랜지 등급, 모든 밸브와 계기, 안전밸브의 크기와 설정압력, 동력기계와 장치의 주요 명세, 계측제어 시스템과의 상호관계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;쓰임&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공정을 이해한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짓고 운전한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;물질 및 열수지&lt;/strong&gt;는 &lt;strong&gt;공정흐름도(PFD)&lt;/strong&gt;에 담는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PFD와 P&amp;amp;ID&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공정흐름도(PFD)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공정배관계장도(P&amp;amp;ID)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;무엇&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공정의 큰 흐름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;배관과 계기까지 낱낱이&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;담는 것&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물질수지 · 열수지 · 운전온도와 압력 · 주요 장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 배관의 호칭지름·재질·플랜지 등급, 모든 밸브와 계기, 안전밸브의 크기와 설정압력, 동력기계와 장치의 주요 명세, 계측제어 시스템과의 상호관계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;쓰임&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공정을 이해한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짓고 운전한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH96" s="32" t="inlineStr">
         <is>
-          <t>② 안전밸브의 크기와 설정압력은 P&amp;amp;ID 에 표시한다.&lt;br&gt;③ 동력기계와 장치의 주요 명세도 그렇다.&lt;br&gt;④ 계측제어 시스템과의 상호관계도 그렇다.</t>
+          <t>② 안전밸브의 크기와 설정압력은 P&amp;amp;ID에 표시한다.&lt;br&gt;③ 동력기계와 장치의 주요 명세도 그렇다.&lt;br&gt;④ 계측제어 시스템과의 상호관계도 그렇다.</t>
         </is>
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공정배관계장도(P&amp;amp;ID)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PFD 는 「무엇이 얼마나 흐르나」, P&amp;amp;ID 는 「어떤 관과 계기로 흐르나」&lt;/strong&gt;다. &lt;strong&gt;수지(收支)라는 말이 나오면 PFD&lt;/strong&gt;로 보내면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;물질·열수지는 PFD&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공정배관계장도(P&amp;amp;ID)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PFD는 「무엇이 얼마나 흐르나」, P&amp;amp;ID는 「어떤 관과 계기로 흐르나」&lt;/strong&gt;다. &lt;strong&gt;수지(收支)라는 말이 나오면 PFD&lt;/strong&gt;로 보내면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;물질·열수지는 PFD&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13968,12 +13968,12 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>절대온도로 $T_{1} = 559.67$, $T_{2} = 1 {,} 534.67$ [R] 이다. $\dfrac{T_{2}}{T_{1}} = ( \dfrac{P_{2}}{P_{1}} )^{\dfrac{k - 1}{k}}$ 이므로 $P_{2} = ( 2.742 )^{3.5} \fallingdotseq 34.1$ [atm] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;단열압축&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단열과정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{T_{2}}{T_{1}} = ( \dfrac{P_{2}}{P_{1}} )^{\dfrac{k - 1}{k}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력으로 풀면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{2} = P_{1} ( \dfrac{T_{2}}{T_{1}} )^{\dfrac{k}{k - 1}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;k = 1.4 이면 지수가 3.5&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;랭킨온도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[R] = ℉ + 459.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;절대온도로 바꿔야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그 압력을 넘기면 자동발화점에 닿는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>절대온도로 $T_{1} = 559.67$, $T_{2} = 1 {,} 534.67$ [R]이다. $\dfrac{T_{2}}{T_{1}} = ( \dfrac{P_{2}}{P_{1}} )^{\dfrac{k - 1}{k}}$이므로 $P_{2} = ( 2.742 )^{3.5} \fallingdotseq 34.1$ [atm]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;단열압축&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단열과정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{T_{2}}{T_{1}} = ( \dfrac{P_{2}}{P_{1}} )^{\dfrac{k - 1}{k}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력으로 풀면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{2} = P_{1} ( \dfrac{T_{2}}{T_{1}} )^{\dfrac{k}{k - 1}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;k = 1.4 이면 지수가 3.5&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;랭킨온도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[R] = ℉ + 459.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;절대온도로 바꿔야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그 압력을 넘기면 자동발화점에 닿는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
         <is>
-          <t>① 14.62 [atm] 는 계산과 맞지 않는다.&lt;br&gt;② 24.23 [atm] 도 그렇다.&lt;br&gt;④ 44.62 [atm] 도 그렇다.</t>
+          <t>① 14.62 [atm]는 계산과 맞지 않는다.&lt;br&gt;② 24.23 [atm] 도 그렇다.&lt;br&gt;④ 44.62 [atm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI100" s="32" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가스의 연소&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기체는 이미 기체라 증발할 것도 분해할 것도 없다&lt;/strong&gt; — &lt;strong&gt;남은 것은 「섞이며 타느냐(확산) 섞여 있다 타느냐(예혼합)」&lt;/strong&gt; 뿐이다. &lt;strong&gt;실제 가스기구는 대부분 확산연소&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가스는 확산연소&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가스의 연소&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기체는 이미 기체라 증발할 것도 분해할 것도 없다&lt;/strong&gt; — &lt;strong&gt;남은 것은 「섞이며 타느냐(확산) 섞여 있다 타느냐(예혼합)」&lt;/strong&gt;뿐이다. &lt;strong&gt;실제 가스기구는 대부분 확산연소&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가스는 확산연소&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>$\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow C_{2} H_{2} + \mathrm{Ca} ( OH )_{2}$ 다. &lt;strong&gt;아세틸렌&lt;/strong&gt;이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;물과 반응해 가스를 내는 물질&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;나오는 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화칼슘(CaC₂)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 카바이드&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나트륨 · 칼륨 · 리튬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화알루미늄(Al₄C₃)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화칼슘(Ca₃P₂)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;포스핀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소화나트륨(NaH)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\mathrm{CaC}_{2} + 2 H_{2} O \rightarrow C_{2} H_{2} + \mathrm{Ca} ( OH )_{2}$다. &lt;strong&gt;아세틸렌&lt;/strong&gt;이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;물과 반응해 가스를 내는 물질&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;나오는 가스&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화칼슘(CaC₂)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 카바이드&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나트륨 · 칼륨 · 리튬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄화알루미늄(Al₄C₃)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;메탄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화칼슘(Ca₃P₂)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;포스핀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소화나트륨(NaH)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="AI102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;탄화칼슘(카바이드)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 폭발범위가 2.5 ~ 81 [vol%] 로 대단히 넓다&lt;/strong&gt; — &lt;strong&gt;카바이드에 물이 스미면 곧 폭발분위기&lt;/strong&gt;가 된다. &lt;strong&gt;카바이드는 밀폐용기에 넣어 물기 없는 곳에 저장&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;카바이드 + 물 = 아세틸렌&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;탄화칼슘(카바이드)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 폭발범위가 2.5 ~ 81 [vol%]로 대단히 넓다&lt;/strong&gt; — &lt;strong&gt;카바이드에 물이 스미면 곧 폭발분위기&lt;/strong&gt;가 된다. &lt;strong&gt;카바이드는 밀폐용기에 넣어 물기 없는 곳에 저장&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;카바이드 + 물 = 아세틸렌&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14743,12 +14743,12 @@
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>② 1.5 [m] 는 규정된 값이 아니다.&lt;br&gt;③ 2.0 [m] 도 그렇다.&lt;br&gt;④ 2.5 [m] 도 그렇다.</t>
+          <t>② 1.5 [m]는 규정된 값이 아니다.&lt;br&gt;③ 2.0 [m] 도 그렇다.&lt;br&gt;④ 2.5 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;트렌치 굴착&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;트렌치는 좁고 깊어 무너지면 빠져나올 수 없다&lt;/strong&gt; — &lt;strong&gt;폭 1 [m] 는 「사람이 몸을 돌려 대피할 수 있는가」&lt;/strong&gt;를 잡은 값이다. &lt;strong&gt;깊이 1.5 [m] 를 넘으면 흙막이 지보공&lt;/strong&gt;이라는 숫자와 짝지어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;깊이 2 [m] 이상이면 폭 1 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;트렌치 굴착&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;트렌치는 좁고 깊어 무너지면 빠져나올 수 없다&lt;/strong&gt; — &lt;strong&gt;폭 1 [m]는 「사람이 몸을 돌려 대피할 수 있는가」&lt;/strong&gt;를 잡은 값이다. &lt;strong&gt;깊이 1.5 [m]를 넘으면 흙막이 지보공&lt;/strong&gt;이라는 숫자와 짝지어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;깊이 2 [m] 이상이면 폭 1 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15130,12 +15130,12 @@
       </c>
       <c r="AH109" s="32" t="inlineStr">
         <is>
-          <t>① 1 : 1 은 연암 및 풍화암의 기울기다.&lt;br&gt;② 1 : 0.8 은 기준에 없는 값이다.&lt;br&gt;④ 1 : 0.3 도 없는 값이다.</t>
+          <t>① 1 : 1은 연암 및 풍화암의 기울기다.&lt;br&gt;② 1 : 0.8은 기준에 없는 값이다.&lt;br&gt;④ 1 : 0.3 도 없는 값이다.</t>
         </is>
       </c>
       <c r="AI109" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;굴착면의 기울기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단단할수록 세우고 무를수록 눕힌다&lt;/strong&gt; — &lt;strong&gt;경암 0.5 → 연암·풍화암 1.0 → 그 밖의 흙 1.2 → 모래 1.8&lt;/strong&gt;로 커진다. &lt;strong&gt;앞의 1 은 높이, 뒤의 숫자가 밑변&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;경암은 1 : 0.5&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021.11.19 개정&lt;/u&gt;으로 &lt;u&gt;풍화암과 연암이 1 : 1.0 으로 통합&lt;/u&gt; 되고 &lt;u&gt;「보통흙」이 「그 밖의 흙 1 : 1.2」로 정리&lt;/u&gt; 되었다. 옛 표(습지 1:1~1:1.5, 건지 1:0.5~1:1, 풍화암 1:1.0, 연암 1:1.0, 경암 1:0.5)로 외워 두지 말 것.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;굴착면의 기울기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단단할수록 세우고 무를수록 눕힌다&lt;/strong&gt; — &lt;strong&gt;경암 0.5 → 연암·풍화암 1.0 → 그 밖의 흙 1.2 → 모래 1.8&lt;/strong&gt;로 커진다. &lt;strong&gt;앞의 1은 높이, 뒤의 숫자가 밑변&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;경암은 1 : 0.5&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021.11.19 개정&lt;/u&gt;으로 &lt;u&gt;풍화암과 연암이 1 : 1.0으로 통합&lt;/u&gt;되고 &lt;u&gt;「보통흙」이 「그 밖의 흙 1 : 1.2」로 정리&lt;/u&gt; 되었다. 옛 표(습지 1:1~1:1.5, 건지 1:0.5~1:1, 풍화암 1:1.0, 연암 1:1.0, 경암 1:0.5)로 외워 두지 말 것.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="AG111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;간극비&lt;/strong&gt;는 흙의 상태를 나타내는 값일 뿐 &lt;strong&gt;안정계산에 직접 들어가지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사면 안정계산에 쓰는 값&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 점착력 c&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전단강도 &lt;/u&gt;$\tau = c + \sigma \tan \phi$&lt;u&gt; 의 항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 내부마찰각 φ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 식의 항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 단위중량 γ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄러지려는 힘(활동력)을 만든다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간극비 e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙의 상태를 나타내는 값 — 계산에 직접 들어가지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;간극비&lt;/strong&gt;는 흙의 상태를 나타내는 값일 뿐 &lt;strong&gt;안정계산에 직접 들어가지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사면 안정계산에 쓰는 값&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 점착력 c&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전단강도 &lt;/u&gt;$\tau = c + \sigma \tan \phi$&lt;u&gt;의 항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 내부마찰각 φ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 식의 항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 단위중량 γ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄러지려는 힘(활동력)을 만든다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간극비 e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙의 상태를 나타내는 값 — 계산에 직접 들어가지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH111" s="32" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="AI111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;사면의 안정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전율은 「버티는 힘(전단강도) ÷ 미끄러지려는 힘」&lt;/strong&gt;이다 — &lt;strong&gt;버티는 쪽이 c 와 φ, 미는 쪽이 단위중량&lt;/strong&gt;이다. &lt;strong&gt;간극비는 그 셋을 거쳐 간접으로만 영향&lt;/strong&gt;을 준다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;c · φ · γ 셋&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;사면의 안정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전율은 「버티는 힘(전단강도) ÷ 미끄러지려는 힘」&lt;/strong&gt;이다 — &lt;strong&gt;버티는 쪽이 c와 φ, 미는 쪽이 단위중량&lt;/strong&gt;이다. &lt;strong&gt;간극비는 그 셋을 거쳐 간접으로만 영향&lt;/strong&gt;을 준다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;c · φ · γ 셋&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15651,7 +15651,7 @@
       </c>
       <c r="AI113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유해위험방지계획서 제출 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「31 · 30,000 · 5,000 · 50 · 2천만 · 10」&lt;/strong&gt; 여섯이다. &lt;strong&gt;냉동·냉장 창고는 건물 자체도 5,000, 설비·단열공사도 5,000&lt;/strong&gt;으로 같다 — &lt;strong&gt;그 하나만 3,000 으로 낮춰 놓은 것&lt;/strong&gt;이 이 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;냉동·냉장 창고 설비·단열은 5,000 [m²]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 제출 대상은 &lt;u&gt;시행령 제42조 제3항&lt;/u&gt;에 있다. 착공 &lt;u&gt;전날&lt;/u&gt;까지 &lt;u&gt;한국산업안전보건공단&lt;/u&gt;에 제출한다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유해위험방지계획서 제출 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「31 · 30,000 · 5,000 · 50 · 2천만 · 10」&lt;/strong&gt; 여섯이다. &lt;strong&gt;냉동·냉장 창고는 건물 자체도 5,000, 설비·단열공사도 5,000&lt;/strong&gt;으로 같다 — &lt;strong&gt;그 하나만 3,000으로 낮춰 놓은 것&lt;/strong&gt;이 이 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;냉동·냉장 창고 설비·단열은 5,000 [m²]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 제출 대상은 &lt;u&gt;시행령 제42조 제3항&lt;/u&gt;에 있다. 착공 &lt;u&gt;전날&lt;/u&gt;까지 &lt;u&gt;한국산업안전보건공단&lt;/u&gt;에 제출한다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="AH114" s="32" t="inlineStr">
         <is>
-          <t>① 30 [cm] 는 기준에 못 미친다.&lt;br&gt;③ 50 [cm] 는 기준보다 넓다.&lt;br&gt;④ 60 [cm] 도 그렇다.</t>
+          <t>① 30 [cm]는 기준에 못 미친다.&lt;br&gt;③ 50 [cm]는 기준보다 넓다.&lt;br&gt;④ 60 [cm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI114" s="32" t="inlineStr">
@@ -16028,17 +16028,17 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>단면적은 $A = \pi \times 75^{2} = 17 {,} 671$ [mm²] 이다. $f = \dfrac{460 {,} 000}{17 {,} 671} \fallingdotseq 26$ [MPa] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;압축강도의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 단면적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A = \dfrac{\pi d^{2}}{4} = \pi \times 75^{2} = 17 {,} 671$ [mm²]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반지름 75 [mm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;460 [kN] = 460,000 [N]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$f = \dfrac{P}{A} = 26$ [MPa]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [MPa] = 1 [N/mm²]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 30 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;셈에 쓰이지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;공시체 규격일 뿐&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>단면적은 $A = \pi \times 75^{2} = 17 {,} 671$ [mm²]이다. $f = \dfrac{460 {,} 000}{17 {,} 671} \fallingdotseq 26$ [MPa]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;압축강도의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 단면적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$A = \dfrac{\pi d^{2}}{4} = \pi \times 75^{2} = 17 {,} 671$ [mm²]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;반지름 75 [mm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;460 [kN] = 460,000 [N]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$f = \dfrac{P}{A} = 26$ [MPa]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [MPa] = 1 [N/mm²]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 30 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;셈에 쓰이지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;공시체 규격일 뿐&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
         <is>
-          <t>① 16.2 [MPa] 는 계산과 맞지 않는다.&lt;br&gt;② 21.5 [MPa] 도 그렇다.&lt;br&gt;④ 31.2 [MPa] 도 그렇다.</t>
+          <t>① 16.2 [MPa]는 계산과 맞지 않는다.&lt;br&gt;② 21.5 [MPa] 도 그렇다.&lt;br&gt;④ 31.2 [MPa] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;콘크리트의 압축강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1 [MPa] = 1 [N/mm²]&lt;/strong&gt;이라는 관계를 쓰면 &lt;strong&gt;N 과 mm 로 통일하는 순간 답이 바로 MPa&lt;/strong&gt;로 나온다. &lt;strong&gt;높이 30 [cm] 는 공시체 규격(지름의 2배)일 뿐 셈에 들어가지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $f = P / A$, 1 [MPa] = 1 [N/mm²].&lt;/p&gt;</t>
+          <t>&lt;strong&gt;콘크리트의 압축강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1 [MPa] = 1 [N/mm²]&lt;/strong&gt;이라는 관계를 쓰면 &lt;strong&gt;N과 mm로 통일하는 순간 답이 바로 MPa&lt;/strong&gt;로 나온다. &lt;strong&gt;높이 30 [cm]는 공시체 규격(지름의 2배)일 뿐 셈에 들어가지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $f = P / A$, 1 [MPa] = 1 [N/mm²].&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16541,12 +16541,12 @@
       </c>
       <c r="AH120" s="32" t="inlineStr">
         <is>
-          <t>① 초당 5 [m] 는 기준에 없다.&lt;br&gt;② 초당 10 [m] 초과는 설치·수리·점검·해체를 멈추는 기준이다.&lt;br&gt;④ 초당 20 [m] 는 기준에 없다.</t>
+          <t>① 초당 5 [m]는 기준에 없다.&lt;br&gt;② 초당 10 [m] 초과는 설치·수리·점검·해체를 멈추는 기준이다.&lt;br&gt;④ 초당 20 [m]는 기준에 없다.</t>
         </is>
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강풍 시 작업중지 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「10 · 15 · 30 · 35」&lt;/strong&gt;다 — &lt;strong&gt;올라가서 하는 일(설치·해체)이 가장 낮은 10, 앉아서 하는 운전이 15&lt;/strong&gt;다. &lt;strong&gt;30 과 35 는 지나간 뒤의 점검과 붕괴 방지&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;운전중지는 15 [m/s] 초과&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 타워크레인 운전작업 중지 기준은 &lt;u&gt;2017.3.3 개정&lt;/u&gt;으로 순간풍속 &lt;u&gt;초당 15 [m] 초과&lt;/u&gt;로 정해졌다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;강풍 시 작업중지 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「10 · 15 · 30 · 35」&lt;/strong&gt;다 — &lt;strong&gt;올라가서 하는 일(설치·해체)이 가장 낮은 10, 앉아서 하는 운전이 15&lt;/strong&gt;다. &lt;strong&gt;30과 35는 지나간 뒤의 점검과 붕괴 방지&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;운전중지는 15 [m/s] 초과&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 타워크레인 운전작업 중지 기준은 &lt;u&gt;2017.3.3 개정&lt;/u&gt;으로 순간풍속 &lt;u&gt;초당 15 [m] 초과&lt;/u&gt;로 정해졌다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
